--- a/sheets/대금율보/검수/회심곡.xlsx
+++ b/sheets/대금율보/검수/회심곡.xlsx
@@ -24547,8 +24547,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -24660,7 +24659,7 @@
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–‹
+–
 林</t>
         </is>
       </c>
@@ -24681,8 +24680,7 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -24916,8 +24914,7 @@
         <is>
           <t xml:space="preserve">汰
 㴌
-–)
-‹</t>
+–)</t>
         </is>
       </c>
       <c r="M6" s="24"/>
@@ -24925,8 +24922,7 @@
         <is>
           <t xml:space="preserve">淋
 湳
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -24936,8 +24932,7 @@
       </c>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="Q6" s="24" t="inlineStr">
@@ -24957,8 +24952,7 @@
         <is>
           <t xml:space="preserve">潢
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -25008,7 +25002,7 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -25066,7 +25060,7 @@
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–‹
+–
 湳</t>
         </is>
       </c>
@@ -25105,7 +25099,7 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -25284,7 +25278,7 @@
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌フ
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -25334,8 +25328,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南)
-‹</t>
+          <t xml:space="preserve">南)</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -25387,8 +25380,7 @@
         <is>
           <t xml:space="preserve">潢
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="U10" s="24" t="inlineStr">
@@ -25503,8 +25495,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C12" s="23"/>
@@ -25522,8 +25513,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -25611,7 +25601,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南)
-–‹
+–
 林</t>
         </is>
       </c>
@@ -25644,8 +25634,7 @@
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-‹</t>
+          <t xml:space="preserve">潢ʒ</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">
@@ -25717,7 +25706,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–‹
+–
 汰И</t>
         </is>
       </c>
@@ -25757,7 +25746,7 @@
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 潢</t>
         </is>
       </c>
@@ -25768,8 +25757,7 @@
       </c>
       <c r="R14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∧
-‹</t>
+          <t xml:space="preserve">淋∧</t>
         </is>
       </c>
       <c r="S14" s="24"/>
@@ -25777,8 +25765,7 @@
         <is>
           <t xml:space="preserve">林
 –
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="U14" s="24" t="inlineStr">
@@ -25899,7 +25886,7 @@
       <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -25923,7 +25910,7 @@
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌)
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -25935,7 +25922,7 @@
       <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌フ
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -25968,8 +25955,7 @@
         <is>
           <t xml:space="preserve">南
 林
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="O16" s="23" t="inlineStr">
@@ -26002,7 +25988,7 @@
       <c r="T16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌フ
-–‹
+–
 h</t>
         </is>
       </c>
@@ -26017,7 +26003,7 @@
       <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -26060,8 +26046,7 @@
         <is>
           <t xml:space="preserve">淋∧
 湳)
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="23"/>
@@ -26261,8 +26246,7 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="E21" s="22"/>
@@ -26316,8 +26300,7 @@
       </c>
       <c r="N21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="O21" s="22"/>
@@ -26408,8 +26391,7 @@
       </c>
       <c r="J22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="K22" s="23"/>
@@ -26452,7 +26434,7 @@
       <c r="R22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -26508,8 +26490,7 @@
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="I23" s="23"/>
@@ -26570,7 +26551,7 @@
       <c r="T23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌フ
-–‹
+–
 h</t>
         </is>
       </c>
@@ -26584,8 +26565,7 @@
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="C24" s="24"/>
@@ -26652,7 +26632,7 @@
       <c r="N24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–‹
+–
 И</t>
         </is>
       </c>
@@ -26660,7 +26640,7 @@
       <c r="P24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -26854,7 +26834,7 @@
       <c r="H26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌)
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -26879,8 +26859,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M26" s="23" t="inlineStr">
@@ -26903,7 +26882,7 @@
       <c r="P26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -26951,8 +26930,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -27085,8 +27063,7 @@
       </c>
       <c r="H28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="I28" s="24"/>
@@ -27094,8 +27071,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K28" s="24" t="inlineStr">
@@ -27118,7 +27094,7 @@
       <c r="N28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 潢</t>
         </is>
       </c>
@@ -27279,8 +27255,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -27444,7 +27419,7 @@
       <c r="J31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -27499,8 +27474,7 @@
       </c>
       <c r="T31" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="U31" s="23"/>
@@ -27533,8 +27507,7 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="G32" s="24"/>
@@ -27565,7 +27538,7 @@
       <c r="L32" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–‹
+–
 林</t>
         </is>
       </c>
@@ -27719,8 +27692,7 @@
       </c>
       <c r="R33" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="S33" s="22"/>
@@ -27779,8 +27751,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -27941,8 +27912,7 @@
       </c>
       <c r="P35" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="Q35" s="23"/>
@@ -28036,7 +28006,7 @@
       <c r="L36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌)
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -28047,8 +28017,7 @@
       </c>
       <c r="N36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="O36" s="24"/>
@@ -28124,7 +28093,7 @@
       <c r="B39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -28135,8 +28104,7 @@
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="E39" s="22"/>
@@ -28154,8 +28122,7 @@
       </c>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="I39" s="22"/>
@@ -28294,8 +28261,7 @@
         <is>
           <t xml:space="preserve">–
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M40" s="23" t="inlineStr">
@@ -28380,8 +28346,7 @@
       </c>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="G41" s="23"/>
@@ -28471,7 +28436,7 @@
       <c r="B42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–‹
+–
 林</t>
         </is>
       </c>
@@ -28520,8 +28485,7 @@
         <is>
           <t xml:space="preserve">–
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K42" s="24" t="inlineStr">
@@ -28578,7 +28542,7 @@
       <c r="T42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌)
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -28719,8 +28683,7 @@
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
@@ -28803,7 +28766,7 @@
       <c r="R44" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -28814,8 +28777,7 @@
       </c>
       <c r="T44" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="U44" s="23"/>
@@ -28862,8 +28824,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I45" s="23" t="inlineStr">
@@ -29178,8 +29139,7 @@
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="C48" s="23"/>
@@ -29255,8 +29215,7 @@
       </c>
       <c r="P48" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="Q48" s="23"/>
@@ -29312,7 +29271,7 @@
       <c r="F49" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南)
-–‹
+–
 林</t>
         </is>
       </c>
@@ -29506,8 +29465,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="U50" s="24" t="inlineStr">
@@ -29701,8 +29659,7 @@
         <is>
           <t xml:space="preserve">–
 И
-㴌)
-‹</t>
+㴌)</t>
         </is>
       </c>
       <c r="M52" s="23"/>
@@ -29734,8 +29691,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="S52" s="23" t="inlineStr">
@@ -29857,7 +29813,7 @@
       <c r="R53" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -30095,7 +30051,7 @@
       <c r="N57" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 湳</t>
         </is>
       </c>
@@ -30293,7 +30249,7 @@
       <c r="N59" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌)
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -30317,7 +30273,7 @@
       <c r="R59" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -30486,15 +30442,14 @@
       </c>
       <c r="N61" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="O61" s="22"/>
       <c r="P61" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -30538,8 +30493,7 @@
         <is>
           <t xml:space="preserve">汰
 㴌
-–汰
-‹</t>
+–汰</t>
         </is>
       </c>
       <c r="G62" s="23" t="inlineStr">
@@ -30551,8 +30505,7 @@
         <is>
           <t xml:space="preserve">潢
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I62" s="23" t="inlineStr">
@@ -30562,8 +30515,7 @@
       </c>
       <c r="J62" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰)
-‹</t>
+          <t xml:space="preserve">汰)</t>
         </is>
       </c>
       <c r="K62" s="23" t="inlineStr">
@@ -30674,8 +30626,7 @@
       </c>
       <c r="L63" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="M63" s="23"/>
@@ -30993,7 +30944,7 @@
       <c r="T66" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–‹
+–
 淋</t>
         </is>
       </c>
@@ -31149,7 +31100,7 @@
       <c r="N68" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 㴌</t>
         </is>
       </c>
@@ -31184,8 +31135,7 @@
       </c>
       <c r="T68" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="U68" s="24"/>
@@ -31367,8 +31317,7 @@
       </c>
       <c r="R70" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌)
-‹</t>
+          <t xml:space="preserve">㴌)</t>
         </is>
       </c>
       <c r="S70" s="23"/>

--- a/sheets/대금율보/검수/회심곡.xlsx
+++ b/sheets/대금율보/검수/회심곡.xlsx
@@ -24491,32 +24491,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="114.74" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="114.74" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="114.74" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="114.74" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="114.74" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="114.74" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="114.74" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="114.74" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="114.74" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="25" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="114.74" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="114.74" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="114.74" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="114.74" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="114.74" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="114.74" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="114.74" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -26200,10 +26200,10 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="102.56" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="114.74" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="114.74" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
       </c>
       <c r="U22" s="23"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="114.74" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="114.74" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="114.74" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="114.74" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
       </c>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="114.74" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="114.74" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="114.74" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="114.74" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="114.74" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
       </c>
       <c r="U31" s="23"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="114.74" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="114.74" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="114.74" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="114.74" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="114.74" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -28058,10 +28058,10 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="6.0" customHeight="true">
       <c r="A37" s="0"/>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="102.56" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="20" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
       <c r="T38" s="20"/>
       <c r="U38" s="20"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="114.74" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
       </c>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="114.74" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="114.74" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="114.74" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="114.74" customHeight="true">
       <c r="A43" s="0"/>
       <c r="B43" s="21" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="56" customHeight="1">
+    <row r="44" ht="114.74" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="21" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
       </c>
       <c r="U44" s="23"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="114.74" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="114.74" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="114.74" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="114.74" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="114.74" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="114.74" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="114.74" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="114.74" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="114.74" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="114.74" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21" t="inlineStr">
         <is>
@@ -29958,10 +29958,10 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="6.0" customHeight="true">
       <c r="A55" s="0"/>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="102.56" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="20" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
       <c r="T56" s="20"/>
       <c r="U56" s="20"/>
     </row>
-    <row r="57" ht="56" customHeight="1">
+    <row r="57" ht="114.74" customHeight="true">
       <c r="A57" s="0"/>
       <c r="B57" s="21"/>
       <c r="C57" s="22"/>
@@ -30097,7 +30097,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="56" customHeight="1">
+    <row r="58" ht="114.74" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="21"/>
       <c r="C58" s="23"/>
@@ -30194,7 +30194,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="114.74" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21"/>
       <c r="C59" s="23"/>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="114.74" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21"/>
       <c r="C60" s="24"/>
@@ -30394,7 +30394,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="56" customHeight="1">
+    <row r="61" ht="114.74" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21"/>
       <c r="C61" s="22"/>
@@ -30483,7 +30483,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="56" customHeight="1">
+    <row r="62" ht="114.74" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21"/>
       <c r="C62" s="23"/>
@@ -30584,7 +30584,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="114.74" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21"/>
       <c r="C63" s="23"/>
@@ -30675,7 +30675,7 @@
       </c>
       <c r="U63" s="23"/>
     </row>
-    <row r="64" ht="56" customHeight="1">
+    <row r="64" ht="114.74" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21"/>
       <c r="C64" s="24"/>
@@ -30772,7 +30772,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="114.74" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21"/>
       <c r="C65" s="22"/>
@@ -30857,7 +30857,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="114.74" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21"/>
       <c r="C66" s="23"/>
@@ -30954,7 +30954,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="114.74" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21"/>
       <c r="C67" s="23"/>
@@ -31051,7 +31051,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="114.74" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21"/>
       <c r="C68" s="24"/>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="U68" s="24"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="114.74" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21"/>
       <c r="C69" s="22"/>
@@ -31241,7 +31241,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="114.74" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21"/>
       <c r="C70" s="23"/>
@@ -31334,7 +31334,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="56" customHeight="1">
+    <row r="71" ht="114.74" customHeight="true">
       <c r="A71" s="0"/>
       <c r="B71" s="21"/>
       <c r="C71" s="23"/>
@@ -31427,7 +31427,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="56" customHeight="1">
+    <row r="72" ht="114.74" customHeight="true">
       <c r="A72" s="0"/>
       <c r="B72" s="21"/>
       <c r="C72" s="24"/>
@@ -31523,7 +31523,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="18" max="16383" man="1"/>
     <brk id="36" max="16383" man="1"/>
